--- a/fiche.xlsx
+++ b/fiche.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://abritek-my.sharepoint.com/personal/admin_hi-inc_ca/Documents/Documents/Projets/Projet 3D/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://abritek-my.sharepoint.com/personal/impressionh3d_abritek_ca/Documents/Desktop/Horizon 3D Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="8_{D68FD718-BF33-4286-9DF1-3BBCA0A5FB3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F8E403F-5D87-4F03-A807-97275980D715}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="8_{D68FD718-BF33-4286-9DF1-3BBCA0A5FB3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23AA1EC1-3E9F-4CEC-868F-BA122086F328}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{31E8DCCF-A35D-453B-82A4-82C70C38F388}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="44">
   <si>
     <t>Matériel</t>
   </si>
@@ -178,26 +178,26 @@
     <t>Port dû</t>
   </si>
   <si>
-    <t>Numéro de Référence Interne (Optionel)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Notes particulières: </t>
   </si>
   <si>
-    <t>Numéro de PO (si désiré)</t>
-  </si>
-  <si>
     <t>Joindre à ce document le dessin de votre pièce en format .STL</t>
   </si>
   <si>
     <t>Même que livraison</t>
+  </si>
+  <si>
+    <t>Numéro de Référence Interne (Optionnel)</t>
+  </si>
+  <si>
+    <t>Numéro de PO (Optionnel)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -237,11 +237,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
       <i/>
       <sz val="8"/>
       <color theme="1"/>
@@ -501,6 +496,26 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0"/>
@@ -509,6 +524,16 @@
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
@@ -526,19 +551,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -547,245 +564,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="29">
+  <dxfs count="10">
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="darkUp">
           <fgColor auto="1"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="darkUp">
-          <fgColor auto="1"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <gradientFill degree="45">
-          <stop position="0">
-            <color theme="0"/>
-          </stop>
-          <stop position="0.5">
-            <color theme="1"/>
-          </stop>
-          <stop position="1">
-            <color theme="0"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="0"/>
         </patternFill>
       </fill>
@@ -894,6 +684,22 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -985,12 +791,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{368E69A0-4097-4AA7-9C64-477E8C650336}" name="Table5" displayName="Table5" ref="B2:D3" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{368E69A0-4097-4AA7-9C64-477E8C650336}" name="Table5" displayName="Table5" ref="B2:D3" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
   <autoFilter ref="B2:D3" xr:uid="{368E69A0-4097-4AA7-9C64-477E8C650336}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{138FD5E2-D6FC-460E-8557-E46B4635382C}" name="Matériel" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{25D0942D-BF70-4177-ADD4-E08BE681EEE9}" name="Finition" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{3E2616B4-9016-4E0F-8BA5-5B404E270D49}" name="Résistance" dataDxfId="25"/>
+    <tableColumn id="1" xr3:uid="{138FD5E2-D6FC-460E-8557-E46B4635382C}" name="Matériel" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{25D0942D-BF70-4177-ADD4-E08BE681EEE9}" name="Finition" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{3E2616B4-9016-4E0F-8BA5-5B404E270D49}" name="Résistance" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1150,7 +956,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{9C906C6C-D50A-4D79-92BD-775B657F73A2}" name="Table8" displayName="Table8" ref="L3:L5" totalsRowShown="0">
   <autoFilter ref="L3:L5" xr:uid="{9C906C6C-D50A-4D79-92BD-775B657F73A2}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{E9B12944-884C-4373-9A7F-5C1B3B0DAA9A}" name="PETG" dataDxfId="24"/>
+    <tableColumn id="1" xr3:uid="{E9B12944-884C-4373-9A7F-5C1B3B0DAA9A}" name="PETG" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1529,121 +1335,121 @@
       <c r="B5" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="17"/>
+      <c r="D5" s="23"/>
     </row>
     <row r="7" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
     </row>
     <row r="8" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B8" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
     </row>
     <row r="9" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
     </row>
     <row r="10" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B10" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
     </row>
     <row r="11" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B11" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
     </row>
     <row r="12" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
     </row>
     <row r="13" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
     </row>
     <row r="14" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
     </row>
     <row r="15" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="22"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
     </row>
     <row r="16" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
     </row>
     <row r="17" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
     </row>
     <row r="18" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="35" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
+      <c r="B18" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
     </row>
     <row r="19" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="36"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
+      <c r="B19" s="33"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
     </row>
     <row r="20" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B20" s="20"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
     </row>
     <row r="21" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="26" t="s">
+      <c r="C21" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="26"/>
+      <c r="D21" s="21"/>
     </row>
     <row r="22" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
     </row>
     <row r="23" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B23" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
     </row>
     <row r="26" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B26" s="10" t="s">
@@ -1654,71 +1460,62 @@
     </row>
     <row r="27" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B27" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C27" s="30"/>
+        <v>43</v>
+      </c>
+      <c r="C27" s="16"/>
       <c r="D27" s="15"/>
     </row>
     <row r="28" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B28" s="10" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="14"/>
     </row>
     <row r="29" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="32" t="s">
+      <c r="B29" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="24"/>
+      <c r="D29" s="25"/>
+    </row>
+    <row r="30" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="26"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+    </row>
+    <row r="31" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="27"/>
+      <c r="C31" s="27"/>
+      <c r="D31" s="27"/>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B32" s="27"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="27"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B33" s="27"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="27"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B34" s="27"/>
+      <c r="C34" s="27"/>
+      <c r="D34" s="27"/>
+    </row>
+    <row r="39" spans="1:5" ht="21" x14ac:dyDescent="0.25">
+      <c r="A39" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="33"/>
-      <c r="D29" s="34"/>
-    </row>
-    <row r="30" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="31"/>
-      <c r="C30" s="31"/>
-      <c r="D30" s="31"/>
-    </row>
-    <row r="31" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-    </row>
-    <row r="39" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A39" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="23"/>
-      <c r="C39" s="23"/>
-      <c r="D39" s="23"/>
-      <c r="E39" s="23"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" selectLockedCells="1"/>
   <mergeCells count="23">
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C21:D21"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="B30:D34"/>
@@ -1733,9 +1530,18 @@
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C21:D21"/>
   </mergeCells>
   <conditionalFormatting sqref="C3 D3">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>ISBLANK($B$3)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1801,6 +1607,35 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="3" id="{CF24EF0E-8CDC-47F6-A425-607AFAE9768F}">
+            <xm:f>IF($C$5=Listes!$N$13,1,0)</xm:f>
+            <x14:dxf>
+              <font>
+                <color theme="0"/>
+              </font>
+              <fill>
+                <patternFill patternType="none">
+                  <bgColor auto="1"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="expression" priority="7" id="{5AC53673-C496-4FF7-A83B-42D35541C3E0}">
+            <xm:f>IF($C$5=Listes!$N$11,1,0)</xm:f>
+            <x14:dxf>
+              <font>
+                <color theme="0"/>
+              </font>
+              <fill>
+                <patternFill patternType="none">
+                  <bgColor auto="1"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B11:B14 C13:C15 B16 B17:C18 C19 B20</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="expression" priority="6" id="{417E2809-6959-40C1-BDB9-242AF1AFD08A}">
             <xm:f>IF(NOT($C$21=Listes!$P$12),1,0)</xm:f>
             <x14:dxf>
@@ -1815,35 +1650,6 @@
             </x14:dxf>
           </x14:cfRule>
           <xm:sqref>B22:C23</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="7" id="{5AC53673-C496-4FF7-A83B-42D35541C3E0}">
-            <xm:f>IF($C$5=Listes!$N$11,1,0)</xm:f>
-            <x14:dxf>
-              <font>
-                <color theme="0"/>
-              </font>
-              <fill>
-                <patternFill patternType="none">
-                  <bgColor auto="1"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="3" id="{CF24EF0E-8CDC-47F6-A425-607AFAE9768F}">
-            <xm:f>IF($C$5=Listes!$N$13,1,0)</xm:f>
-            <x14:dxf>
-              <font>
-                <color theme="0"/>
-              </font>
-              <fill>
-                <patternFill patternType="none">
-                  <bgColor auto="1"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B17:C18 C13:C15 B11:B14 B20 B16 C19</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -1873,25 +1679,25 @@
   <sheetData>
     <row r="1" spans="2:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H2" s="27" t="s">
+      <c r="H2" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="28"/>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="28"/>
-      <c r="S2" s="28"/>
-      <c r="T2" s="28"/>
-      <c r="U2" s="28"/>
-      <c r="V2" s="28"/>
-      <c r="W2" s="28"/>
-      <c r="X2" s="29"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
+      <c r="X2" s="36"/>
     </row>
     <row r="3" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
@@ -2010,7 +1816,9 @@
       <c r="F6" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="8"/>
+      <c r="H6" s="8" t="s">
+        <v>14</v>
+      </c>
       <c r="X6" s="2"/>
     </row>
     <row r="7" spans="2:26" x14ac:dyDescent="0.25">

--- a/fiche.xlsx
+++ b/fiche.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://abritek-my.sharepoint.com/personal/impressionh3d_abritek_ca/Documents/Desktop/Horizon 3D Website/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://abritek-my.sharepoint.com/personal/admin_hi-inc_ca/Documents/Documents/Projets/Projet 3D/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="8_{D68FD718-BF33-4286-9DF1-3BBCA0A5FB3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23AA1EC1-3E9F-4CEC-868F-BA122086F328}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="8_{D68FD718-BF33-4286-9DF1-3BBCA0A5FB3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F8E403F-5D87-4F03-A807-97275980D715}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{31E8DCCF-A35D-453B-82A4-82C70C38F388}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="44">
   <si>
     <t>Matériel</t>
   </si>
@@ -178,26 +178,26 @@
     <t>Port dû</t>
   </si>
   <si>
+    <t>Numéro de Référence Interne (Optionel)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Notes particulières: </t>
   </si>
   <si>
+    <t>Numéro de PO (si désiré)</t>
+  </si>
+  <si>
     <t>Joindre à ce document le dessin de votre pièce en format .STL</t>
   </si>
   <si>
     <t>Même que livraison</t>
-  </si>
-  <si>
-    <t>Numéro de Référence Interne (Optionnel)</t>
-  </si>
-  <si>
-    <t>Numéro de PO (Optionnel)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -237,6 +237,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="8"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
       <i/>
       <sz val="8"/>
       <color theme="1"/>
@@ -496,11 +501,30 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -516,66 +540,252 @@
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="29">
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="darkUp">
           <fgColor auto="1"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="darkUp">
+          <fgColor auto="1"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="0.5">
+            <color theme="1"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="0"/>
         </patternFill>
       </fill>
@@ -621,22 +831,6 @@
         <vertical/>
         <horizontal/>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -791,12 +985,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{368E69A0-4097-4AA7-9C64-477E8C650336}" name="Table5" displayName="Table5" ref="B2:D3" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{368E69A0-4097-4AA7-9C64-477E8C650336}" name="Table5" displayName="Table5" ref="B2:D3" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27">
   <autoFilter ref="B2:D3" xr:uid="{368E69A0-4097-4AA7-9C64-477E8C650336}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{138FD5E2-D6FC-460E-8557-E46B4635382C}" name="Matériel" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{25D0942D-BF70-4177-ADD4-E08BE681EEE9}" name="Finition" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{3E2616B4-9016-4E0F-8BA5-5B404E270D49}" name="Résistance" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{138FD5E2-D6FC-460E-8557-E46B4635382C}" name="Matériel" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{25D0942D-BF70-4177-ADD4-E08BE681EEE9}" name="Finition" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{3E2616B4-9016-4E0F-8BA5-5B404E270D49}" name="Résistance" dataDxfId="25"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -956,7 +1150,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{9C906C6C-D50A-4D79-92BD-775B657F73A2}" name="Table8" displayName="Table8" ref="L3:L5" totalsRowShown="0">
   <autoFilter ref="L3:L5" xr:uid="{9C906C6C-D50A-4D79-92BD-775B657F73A2}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{E9B12944-884C-4373-9A7F-5C1B3B0DAA9A}" name="PETG" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{E9B12944-884C-4373-9A7F-5C1B3B0DAA9A}" name="PETG" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1335,121 +1529,121 @@
       <c r="B5" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="23"/>
+      <c r="D5" s="17"/>
     </row>
     <row r="7" spans="2:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
     </row>
     <row r="8" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B8" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
     </row>
     <row r="9" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
     </row>
     <row r="10" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B10" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
     </row>
     <row r="11" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B11" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
     </row>
     <row r="12" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
     </row>
     <row r="13" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
     </row>
     <row r="14" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
     </row>
     <row r="15" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="31"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
     </row>
     <row r="16" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
     </row>
     <row r="17" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
     </row>
     <row r="18" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
+      <c r="B18" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
     </row>
     <row r="19" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="33"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
     </row>
     <row r="20" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
     </row>
     <row r="21" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="21" t="s">
+      <c r="C21" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="21"/>
+      <c r="D21" s="26"/>
     </row>
     <row r="22" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
     </row>
     <row r="23" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B23" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
     </row>
     <row r="26" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B26" s="10" t="s">
@@ -1460,62 +1654,71 @@
     </row>
     <row r="27" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B27" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" s="16"/>
+        <v>41</v>
+      </c>
+      <c r="C27" s="30"/>
       <c r="D27" s="15"/>
     </row>
     <row r="28" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B28" s="10" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="14"/>
     </row>
     <row r="29" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="C29" s="24"/>
-      <c r="D29" s="25"/>
+      <c r="B29" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" s="33"/>
+      <c r="D29" s="34"/>
     </row>
     <row r="30" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="26"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
+      <c r="B30" s="31"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
     </row>
     <row r="31" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="27"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B32" s="27"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B33" s="27"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="27"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B34" s="27"/>
-      <c r="C34" s="27"/>
-      <c r="D34" s="27"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
     </row>
     <row r="39" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A39" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="18"/>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
+      <c r="A39" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="23"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" selectLockedCells="1"/>
   <mergeCells count="23">
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C21:D21"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="B30:D34"/>
@@ -1530,18 +1733,9 @@
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C15:D15"/>
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C21:D21"/>
   </mergeCells>
   <conditionalFormatting sqref="C3 D3">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>ISBLANK($B$3)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1607,35 +1801,6 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="3" id="{CF24EF0E-8CDC-47F6-A425-607AFAE9768F}">
-            <xm:f>IF($C$5=Listes!$N$13,1,0)</xm:f>
-            <x14:dxf>
-              <font>
-                <color theme="0"/>
-              </font>
-              <fill>
-                <patternFill patternType="none">
-                  <bgColor auto="1"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="7" id="{5AC53673-C496-4FF7-A83B-42D35541C3E0}">
-            <xm:f>IF($C$5=Listes!$N$11,1,0)</xm:f>
-            <x14:dxf>
-              <font>
-                <color theme="0"/>
-              </font>
-              <fill>
-                <patternFill patternType="none">
-                  <bgColor auto="1"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B11:B14 C13:C15 B16 B17:C18 C19 B20</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="expression" priority="6" id="{417E2809-6959-40C1-BDB9-242AF1AFD08A}">
             <xm:f>IF(NOT($C$21=Listes!$P$12),1,0)</xm:f>
             <x14:dxf>
@@ -1650,6 +1815,35 @@
             </x14:dxf>
           </x14:cfRule>
           <xm:sqref>B22:C23</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="7" id="{5AC53673-C496-4FF7-A83B-42D35541C3E0}">
+            <xm:f>IF($C$5=Listes!$N$11,1,0)</xm:f>
+            <x14:dxf>
+              <font>
+                <color theme="0"/>
+              </font>
+              <fill>
+                <patternFill patternType="none">
+                  <bgColor auto="1"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="expression" priority="3" id="{CF24EF0E-8CDC-47F6-A425-607AFAE9768F}">
+            <xm:f>IF($C$5=Listes!$N$13,1,0)</xm:f>
+            <x14:dxf>
+              <font>
+                <color theme="0"/>
+              </font>
+              <fill>
+                <patternFill patternType="none">
+                  <bgColor auto="1"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B17:C18 C13:C15 B11:B14 B20 B16 C19</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -1679,25 +1873,25 @@
   <sheetData>
     <row r="1" spans="2:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H2" s="34" t="s">
+      <c r="H2" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
-      <c r="T2" s="35"/>
-      <c r="U2" s="35"/>
-      <c r="V2" s="35"/>
-      <c r="W2" s="35"/>
-      <c r="X2" s="36"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="28"/>
+      <c r="V2" s="28"/>
+      <c r="W2" s="28"/>
+      <c r="X2" s="29"/>
     </row>
     <row r="3" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
@@ -1816,9 +2010,7 @@
       <c r="F6" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="8" t="s">
-        <v>14</v>
-      </c>
+      <c r="H6" s="8"/>
       <c r="X6" s="2"/>
     </row>
     <row r="7" spans="2:26" x14ac:dyDescent="0.25">
